--- a/RelacaoRIAAtrasada_110826.xlsx
+++ b/RelacaoRIAAtrasada_110826.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cristiano\Documents\ProjetosPyton\ROTAS RIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cristiano\Documents\ProjetosPyton\Gestao RIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$3:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$3:$I$118</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="362">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -90,12 +90,6 @@
     <t>D</t>
   </si>
   <si>
-    <t>ALV 0218</t>
-  </si>
-  <si>
-    <t>RUA ALVES GUIMARAES, 218</t>
-  </si>
-  <si>
     <t>K</t>
   </si>
   <si>
@@ -138,9 +132,6 @@
     <t>M</t>
   </si>
   <si>
-    <t>FEVEREIRO</t>
-  </si>
-  <si>
     <t>TURI0459</t>
   </si>
   <si>
@@ -222,12 +213,6 @@
     <t>RUA DR. VEIGA FILHO, 477</t>
   </si>
   <si>
-    <t>BARO0752</t>
-  </si>
-  <si>
-    <t>RUA BARONESA DE ITU, 752</t>
-  </si>
-  <si>
     <t>DOU 0186</t>
   </si>
   <si>
@@ -396,12 +381,6 @@
     <t>RUA PIAUI, 359</t>
   </si>
   <si>
-    <t>PIAU0335</t>
-  </si>
-  <si>
-    <t>RUA PIAUI, 335</t>
-  </si>
-  <si>
     <t>RIBE0384</t>
   </si>
   <si>
@@ -486,9 +465,6 @@
     <t>MONTELE</t>
   </si>
   <si>
-    <t>01047-000</t>
-  </si>
-  <si>
     <t>MAMO0570</t>
   </si>
   <si>
@@ -585,12 +561,6 @@
     <t>AV NOVA CANTAREIRA, 4755</t>
   </si>
   <si>
-    <t>DOMI0041</t>
-  </si>
-  <si>
-    <t>02712-150</t>
-  </si>
-  <si>
     <t>ITAI0098</t>
   </si>
   <si>
@@ -600,15 +570,6 @@
     <t>RUA ITAIQUARA, 98</t>
   </si>
   <si>
-    <t>TAGI0082</t>
-  </si>
-  <si>
-    <t>01156-000</t>
-  </si>
-  <si>
-    <t>RUA TAGIPURU, 82</t>
-  </si>
-  <si>
     <t>APIN1752</t>
   </si>
   <si>
@@ -618,15 +579,6 @@
     <t>RUA APINAJES, 1752</t>
   </si>
   <si>
-    <t>HAVA0533</t>
-  </si>
-  <si>
-    <t>01259-000</t>
-  </si>
-  <si>
-    <t>RUA HAVAI, 533</t>
-  </si>
-  <si>
     <t>FRA  175</t>
   </si>
   <si>
@@ -783,7 +735,385 @@
     <t>SETEMBRO</t>
   </si>
   <si>
-    <t>RELAÇÃO ENDEREÇOS RIA PENDENTES - 03/09/26</t>
+    <t>TABA0469</t>
+  </si>
+  <si>
+    <t>01020-001</t>
+  </si>
+  <si>
+    <t>RUA TABATINGUERA, 469</t>
+  </si>
+  <si>
+    <t>AUGU0007</t>
+  </si>
+  <si>
+    <t>01025-010</t>
+  </si>
+  <si>
+    <t>RUA AUGUSTO SEVERO, 7</t>
+  </si>
+  <si>
+    <t>SAO 0501</t>
+  </si>
+  <si>
+    <t>01229-904</t>
+  </si>
+  <si>
+    <t>RUA SAO VICENTE DE PAULO, 501</t>
+  </si>
+  <si>
+    <t>AIMB2078</t>
+  </si>
+  <si>
+    <t>01258-020</t>
+  </si>
+  <si>
+    <t>RUA AIMBERE, 2078</t>
+  </si>
+  <si>
+    <t>ALFA</t>
+  </si>
+  <si>
+    <t>NEST0196</t>
+  </si>
+  <si>
+    <t>01303-010</t>
+  </si>
+  <si>
+    <t>RUA NESTOR PESTANA, 196</t>
+  </si>
+  <si>
+    <t>BRAS0350</t>
+  </si>
+  <si>
+    <t>01431-000</t>
+  </si>
+  <si>
+    <t>AV BRASIL, 350</t>
+  </si>
+  <si>
+    <t>HUN 1100</t>
+  </si>
+  <si>
+    <t>01455-000</t>
+  </si>
+  <si>
+    <t>RUA HUNGRIA, 1100</t>
+  </si>
+  <si>
+    <t>VERG0415</t>
+  </si>
+  <si>
+    <t>01504-001</t>
+  </si>
+  <si>
+    <t>RUA VERGUEIRO, 415</t>
+  </si>
+  <si>
+    <t>APEN  69</t>
+  </si>
+  <si>
+    <t>01533-000</t>
+  </si>
+  <si>
+    <t>RUA APENINOS, 69</t>
+  </si>
+  <si>
+    <t>MESQ 248</t>
+  </si>
+  <si>
+    <t>01544-010</t>
+  </si>
+  <si>
+    <t>RUA MESQUITA, 248</t>
+  </si>
+  <si>
+    <t>VOLU2361</t>
+  </si>
+  <si>
+    <t>02011-600</t>
+  </si>
+  <si>
+    <t>RUA VOLUNTARIOS DA PATRIA, 2361</t>
+  </si>
+  <si>
+    <t>LEON0874</t>
+  </si>
+  <si>
+    <t>02042-000</t>
+  </si>
+  <si>
+    <t>AV LEONCIO DE MAGALHAES, 874</t>
+  </si>
+  <si>
+    <t>DILE0045</t>
+  </si>
+  <si>
+    <t>02189-050</t>
+  </si>
+  <si>
+    <t>RUA CORONEL DILERMANDO BRISOLLA, 45</t>
+  </si>
+  <si>
+    <t>FRAN 479</t>
+  </si>
+  <si>
+    <t>02259-001</t>
+  </si>
+  <si>
+    <t>AV FRANCISCO RODRIGUES, 479</t>
+  </si>
+  <si>
+    <t>IMI 3065</t>
+  </si>
+  <si>
+    <t>02465-400</t>
+  </si>
+  <si>
+    <t>AV IMIRIM, 3065</t>
+  </si>
+  <si>
+    <t>PRO 0090</t>
+  </si>
+  <si>
+    <t>02510-020</t>
+  </si>
+  <si>
+    <t>RUA PROF. LUCIANO PRATA, 90</t>
+  </si>
+  <si>
+    <t>BRAZ1732</t>
+  </si>
+  <si>
+    <t>02511-000</t>
+  </si>
+  <si>
+    <t>AV BRAZ LEME, 1732</t>
+  </si>
+  <si>
+    <t>INAJ5180</t>
+  </si>
+  <si>
+    <t>02861-190</t>
+  </si>
+  <si>
+    <t>AV INAJAR DE SOUZA, 5180</t>
+  </si>
+  <si>
+    <t>HENR0131</t>
+  </si>
+  <si>
+    <t>03109-000</t>
+  </si>
+  <si>
+    <t>AV HENRY FORD, 131</t>
+  </si>
+  <si>
+    <t>HIPO1495</t>
+  </si>
+  <si>
+    <t>03162-020</t>
+  </si>
+  <si>
+    <t>RUA HIPODROMO, DO, 1495</t>
+  </si>
+  <si>
+    <t>PADR 054</t>
+  </si>
+  <si>
+    <t>03238-050</t>
+  </si>
+  <si>
+    <t>RUA PADRE BRUNO RICCO, 54</t>
+  </si>
+  <si>
+    <t>GAND0298</t>
+  </si>
+  <si>
+    <t>04023-000</t>
+  </si>
+  <si>
+    <t>RUA GANDAVO, 298</t>
+  </si>
+  <si>
+    <t>DESE0100</t>
+  </si>
+  <si>
+    <t>04102-010</t>
+  </si>
+  <si>
+    <t>RUA DES. ARAGAO, 100</t>
+  </si>
+  <si>
+    <t>ANDR0080</t>
+  </si>
+  <si>
+    <t>04165-160</t>
+  </si>
+  <si>
+    <t>PRC ANDRE NUNES, 80</t>
+  </si>
+  <si>
+    <t>NAZ   28</t>
+  </si>
+  <si>
+    <t>04262-000</t>
+  </si>
+  <si>
+    <t>AV NAZARE, 28</t>
+  </si>
+  <si>
+    <t>LUIS0560</t>
+  </si>
+  <si>
+    <t>04344-010</t>
+  </si>
+  <si>
+    <t>AV DR. LUIS ROCHA MIRANDA, 560</t>
+  </si>
+  <si>
+    <t>JOAQ0035</t>
+  </si>
+  <si>
+    <t>04370-020</t>
+  </si>
+  <si>
+    <t>RUA JOAQUIM MORAES, 35</t>
+  </si>
+  <si>
+    <t>NOVA_365</t>
+  </si>
+  <si>
+    <t>04560-000</t>
+  </si>
+  <si>
+    <t>RUA NOVA YORK, 365</t>
+  </si>
+  <si>
+    <t>NOSS 209</t>
+  </si>
+  <si>
+    <t>04685-000</t>
+  </si>
+  <si>
+    <t>AV NOSSA SENHORA DO SABARA, 209</t>
+  </si>
+  <si>
+    <t>ARN 1251</t>
+  </si>
+  <si>
+    <t>04691-060</t>
+  </si>
+  <si>
+    <t>RUA ARNALDO MAGNICCARO, 1251</t>
+  </si>
+  <si>
+    <t>VERB1711</t>
+  </si>
+  <si>
+    <t>04719-002</t>
+  </si>
+  <si>
+    <t>RUA VERBO DIVINO, 1711</t>
+  </si>
+  <si>
+    <t>DAIKEN</t>
+  </si>
+  <si>
+    <t>TANA0124</t>
+  </si>
+  <si>
+    <t>05002-010</t>
+  </si>
+  <si>
+    <t>RUA TANABI, 124</t>
+  </si>
+  <si>
+    <t>PARA0278</t>
+  </si>
+  <si>
+    <t>05006-010</t>
+  </si>
+  <si>
+    <t>RUA PARAGUAÇU, 278</t>
+  </si>
+  <si>
+    <t>SU  1200</t>
+  </si>
+  <si>
+    <t>05016-110</t>
+  </si>
+  <si>
+    <t>AV SUMARE, 1200</t>
+  </si>
+  <si>
+    <t>JOSE 117</t>
+  </si>
+  <si>
+    <t>05337-090</t>
+  </si>
+  <si>
+    <t>RUA JOSE PEREIRA DE CARVALHO, 117</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>CAPO1475</t>
+  </si>
+  <si>
+    <t>05409-003</t>
+  </si>
+  <si>
+    <t>RUA CAPOTE VALENTE, 1475</t>
+  </si>
+  <si>
+    <t>GALE 065</t>
+  </si>
+  <si>
+    <t>05410-030</t>
+  </si>
+  <si>
+    <t>RUA GALENO DE ALMEIDA, 65</t>
+  </si>
+  <si>
+    <t>GUAR0218</t>
+  </si>
+  <si>
+    <t>08280-530</t>
+  </si>
+  <si>
+    <t>RUA GUARUJA DO SUL, 218</t>
+  </si>
+  <si>
+    <t>JEEM 450</t>
+  </si>
+  <si>
+    <t>08295-015</t>
+  </si>
+  <si>
+    <t>AVENIDA JEAN KHOURY FARAH, 450</t>
+  </si>
+  <si>
+    <t>JEES 450</t>
+  </si>
+  <si>
+    <t>CENT0506</t>
+  </si>
+  <si>
+    <t>08410-100</t>
+  </si>
+  <si>
+    <t>RUA CENTRALINA, 506</t>
+  </si>
+  <si>
+    <t>Sem Data</t>
+  </si>
+  <si>
+    <t>RELAÇÃO ENDEREÇOS RIA PENDENTES - 05/09/26</t>
+  </si>
+  <si>
+    <t>OUTUBRO</t>
   </si>
 </sst>
 </file>
@@ -860,7 +1190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -877,27 +1207,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1178,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -1197,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>251</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1226,2153 +1546,2997 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4734004</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="7">
-        <v>5410000</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="F4" s="7">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="I4" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3102002</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="7">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F8" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1258001</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="7">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="6">
-        <v>4734004</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="7">
-        <v>3</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="6">
-        <v>3102002</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="7">
-        <v>4</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>230</v>
+      <c r="G11" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>194</v>
+        <v>324</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>195</v>
+        <v>325</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>130</v>
+      <c r="F12" s="5">
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>143</v>
+        <v>247</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>250</v>
+        <v>21</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1258001</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="B13" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="5">
         <v>1</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>53</v>
+      <c r="G13" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>113</v>
+        <v>11</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C14" s="6">
         <v>3977409</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F14" s="7">
         <v>1</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>130</v>
+        <v>22</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>123</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1231000</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="B16" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="5">
         <v>2</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="G17" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="6">
         <v>1401000</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F18" s="7">
         <v>2</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="6">
+      <c r="H19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="6">
         <v>3711011</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="D20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="7">
         <v>3</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>11</v>
+      <c r="H20" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="5">
+        <v>2</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F24" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="6">
+      <c r="H24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="6">
         <v>4014000</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" s="7" t="s">
+      <c r="D25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F25" s="7">
         <v>3</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="H25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="6">
         <v>4113010</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="D26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F26" s="7">
         <v>5</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="16">
+      <c r="H26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="14">
         <v>5065000</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="9">
+      <c r="D27" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="8">
         <v>1</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G27" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="H27" s="6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>48</v>
+        <v>173</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>131</v>
+        <v>19</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="6">
-        <v>1222020</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="B29" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="5">
         <v>2</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="6">
-        <v>3510040</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F30" s="7">
+      <c r="H30" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="5">
         <v>1</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="6">
-        <v>8131220</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="7">
-        <v>1</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>86</v>
+      <c r="G31" s="4" t="s">
+        <v>247</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="13" t="s">
-        <v>131</v>
+      <c r="F32" s="11" t="s">
+        <v>124</v>
       </c>
       <c r="G32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1222020</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="7">
+        <v>2</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="H33" s="6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>25</v>
+      <c r="B34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="6">
+        <v>3510040</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C35" s="6">
-        <v>3512050</v>
+        <v>8131220</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="F35" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>131</v>
+        <v>16</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>124</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>11</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>114</v>
+        <v>20</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="6">
-        <v>1040000</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" s="7">
-        <v>2</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>10</v>
+      <c r="B38" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="5">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>247</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>187</v>
+        <v>346</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>188</v>
+        <v>347</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>114</v>
+        <v>20</v>
+      </c>
+      <c r="F39" s="5">
+        <v>2</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>25</v>
+        <v>247</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>250</v>
+        <v>21</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" s="6">
-        <v>2410010</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" s="7">
+      <c r="B40" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="5">
         <v>2</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>13</v>
+      <c r="G40" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>113</v>
+        <v>11</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1045020</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" s="7">
-        <v>2</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>18</v>
+      <c r="B41" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="5">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>247</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>114</v>
+        <v>33</v>
+      </c>
+      <c r="F42" s="5">
+        <v>1</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="H42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" s="6">
+        <v>3512050</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="7">
+        <v>2</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B43" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>11</v>
+      <c r="H43" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>232</v>
+        <v>294</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>131</v>
+        <v>29</v>
+      </c>
+      <c r="F44" s="5">
+        <v>4</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>154</v>
+        <v>255</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>131</v>
+        <v>9</v>
+      </c>
+      <c r="F45" s="5">
+        <v>2</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>131</v>
+        <v>29</v>
+      </c>
+      <c r="F46" s="5">
+        <v>1</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1150010</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="B47" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" s="5">
         <v>2</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>113</v>
+      <c r="G47" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="6">
-        <v>1047000</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="7">
-        <v>2</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>23</v>
+      <c r="B48" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>55</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>50</v>
+        <v>207</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>114</v>
+        <v>22</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H49" s="10" t="s">
-        <v>11</v>
+      <c r="H49" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>32</v>
+      <c r="B50" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1040000</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="7">
+        <v>2</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1050000</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" s="7">
+      <c r="B51" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F52" s="5">
+        <v>12</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B53" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F53" s="5">
+        <v>8</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2410010</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54" s="7">
         <v>2</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1050000</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" s="7">
-        <v>2</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="G54" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H52" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C53" s="6">
-        <v>3729030</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F53" s="7">
-        <v>4</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>23</v>
+      <c r="H54" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C55" s="6">
-        <v>4686002</v>
+        <v>1045020</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F55" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>182</v>
+        <v>314</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>183</v>
+        <v>315</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>184</v>
+        <v>316</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>114</v>
+        <v>22</v>
+      </c>
+      <c r="F56" s="5">
+        <v>2</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>250</v>
+        <v>23</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B57" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="6">
-        <v>3114000</v>
-      </c>
-      <c r="D57" s="6" t="s">
+      <c r="B57" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F57" s="7">
-        <v>2</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>32</v>
+      <c r="G57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>113</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>131</v>
+        <v>16</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B59" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" s="6">
-        <v>5660000</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F59" s="7">
-        <v>3</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>113</v>
+      <c r="B59" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="F59" s="5">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>114</v>
+        <v>29</v>
+      </c>
+      <c r="F60" s="5">
+        <v>1</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>250</v>
+      <c r="H60" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
-        <v>122</v>
+        <v>311</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>120</v>
+        <v>312</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>123</v>
+        <v>313</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>114</v>
+        <v>19</v>
+      </c>
+      <c r="F61" s="5">
+        <v>1</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="4" t="s">
-        <v>119</v>
+        <v>215</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>121</v>
+        <v>217</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>114</v>
+        <v>22</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>124</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>11</v>
+        <v>125</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>114</v>
-      </c>
       <c r="G63" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H63" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B64" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C64" s="6">
-        <v>1330000</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="7">
-        <v>3</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H64" s="10" t="s">
+      <c r="B64" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>113</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B65" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G65" s="4" t="s">
+      <c r="B65" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="6">
+        <v>1150010</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="7">
+        <v>2</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B66" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="6">
+        <v>1047000</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" s="7">
+        <v>2</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H65" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I65" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B66" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>11</v>
+      <c r="H66" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>250</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="4" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>131</v>
+        <v>33</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B68" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>23</v>
+      <c r="B68" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="6">
+        <v>1050000</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="7">
+        <v>2</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C69" s="6">
-        <v>1211000</v>
+        <v>1050000</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F69" s="7">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="6" t="s">
         <v>11</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" s="4" t="s">
-        <v>136</v>
+        <v>263</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>138</v>
+        <v>265</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F70" s="13" t="s">
-        <v>114</v>
+      <c r="F70" s="5">
+        <v>1</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I70" s="7" t="s">
-        <v>250</v>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C71" s="6">
-        <v>4321070</v>
+        <v>3729030</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F71" s="7">
+        <v>4</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B72" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="5">
+        <v>14</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B73" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G71" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I71" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B72" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C72" s="6">
-        <v>1331010</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="7">
-        <v>2</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H72" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I72" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B73" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C73" s="6">
-        <v>3026000</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F73" s="7">
-        <v>1</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H73" s="18" t="s">
-        <v>32</v>
+      <c r="H73" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>40</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" s="4" t="s">
-        <v>190</v>
+        <v>248</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>192</v>
+        <v>250</v>
       </c>
       <c r="E74" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74" s="5">
+        <v>1</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B75" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" s="6">
+        <v>4686002</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E75" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B75" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>11</v>
+      <c r="F75" s="7">
+        <v>3</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>250</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B76" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C76" s="6">
-        <v>5005001</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E76" s="7" t="s">
+      <c r="B76" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E76" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76" s="5">
         <v>1</v>
       </c>
-      <c r="G76" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76" s="7" t="s">
-        <v>39</v>
+      <c r="G76" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B77" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C77" s="6">
-        <v>1229001</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="7">
-        <v>2</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I77" s="7" t="s">
-        <v>113</v>
+      <c r="B77" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F77" s="5">
+        <v>1</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="E78" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>131</v>
+        <v>29</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
-        <v>215</v>
+        <v>296</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>216</v>
+        <v>297</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>217</v>
+        <v>298</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F79" s="13" t="s">
-        <v>114</v>
+        <v>33</v>
+      </c>
+      <c r="F79" s="5">
+        <v>1</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B80" s="6" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C80" s="6">
-        <v>1201030</v>
+        <v>3114000</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F80" s="7">
         <v>2</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81" s="4" t="s">
-        <v>243</v>
+        <v>24</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>244</v>
+        <v>195</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F81" s="13" t="s">
-        <v>130</v>
+        <v>22</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>124</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>32</v>
+        <v>13</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
-        <v>246</v>
+        <v>333</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>247</v>
+        <v>334</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>248</v>
+        <v>335</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F82" s="13" t="s">
-        <v>131</v>
+        <v>20</v>
+      </c>
+      <c r="F82" s="5">
+        <v>2</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="H82" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>250</v>
+        <v>13</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B83" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>11</v>
+      <c r="B83" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" s="6">
+        <v>5660000</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" s="7">
+        <v>3</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" s="4" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>146</v>
+        <v>226</v>
       </c>
       <c r="E84" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I84" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B85" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B86" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86" s="5">
+        <v>1</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B87" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B88" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C88" s="6">
+        <v>1330000</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="7">
+        <v>3</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B89" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B90" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B91" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B92" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B93" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F84" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I84" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B85" s="6"/>
-      <c r="C85" s="6">
+      <c r="F93" s="5">
+        <v>11</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B94" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" s="6">
+        <v>1211000</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" s="7">
+        <v>11</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B95" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B96" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C96" s="6">
+        <v>4321070</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F96" s="7">
+        <v>10</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B97" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C97" s="6">
+        <v>1331010</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="7">
+        <v>2</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B98" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="6">
+        <v>3026000</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98" s="7">
+        <v>1</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B99" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F99" s="5">
+        <v>1</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B100" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="5">
+        <v>1</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B101" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F101" s="5">
+        <v>1</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B102" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B103" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C103" s="6">
+        <v>5005001</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F103" s="7">
+        <v>1</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I103" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B104" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C104" s="6">
+        <v>1229001</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="7">
+        <v>2</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B105" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F105" s="5">
+        <v>1</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B106" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="5">
+        <v>3</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B107" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B108" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I108" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B109" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C109" s="6">
+        <v>1201030</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F109" s="7">
+        <v>2</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I109" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B110" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I110" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B111" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B112" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B113" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F113" s="5">
+        <v>1</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B114" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I114" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B115" s="6"/>
+      <c r="C115" s="6">
+        <v>2017010</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115" s="7">
+        <v>2</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B116" s="6"/>
+      <c r="C116" s="6">
+        <v>2712050</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F116" s="7">
+        <v>1</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B117" s="6"/>
+      <c r="C117" s="6">
+        <v>3364010</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F117" s="7">
+        <v>1</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B118" s="6"/>
+      <c r="C118" s="6">
         <v>4208001</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E85" s="7" t="s">
+      <c r="D118" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F118" s="7">
         <v>2</v>
       </c>
-      <c r="G85" s="6" t="s">
+      <c r="G118" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H85" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B86" s="6"/>
-      <c r="C86" s="6">
-        <v>2017010</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F86" s="7">
-        <v>2</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I86" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B87" s="6"/>
-      <c r="C87" s="6">
-        <v>2712050</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F87" s="7">
-        <v>1</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B88" s="6"/>
-      <c r="C88" s="6">
-        <v>3364010</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F88" s="7">
-        <v>1</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>55</v>
+      <c r="H118" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:I8">
+  <autoFilter ref="B3:I118">
     <sortState ref="B4:L60">
       <sortCondition ref="I4:I60" customList="janeiro,fevereiro,março,abril,maio,junho,julho,agosto,setembro,outubro,novembro,dezembro"/>
       <sortCondition ref="H4:H60"/>
     </sortState>
   </autoFilter>
-  <sortState ref="B9:I95">
-    <sortCondition ref="B4:B95" customList="janeiro,fevereiro,março,abril,maio,junho,julho,agosto,setembro,outubro,novembro,dezembro"/>
+  <sortState ref="B4:I123">
+    <sortCondition ref="B4:B123"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
